--- a/ORDER_MGMT/regular_order_mgmt/order_files_BACKUPS/Result_Executed_OrderBook_14to24july2026.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files_BACKUPS/Result_Executed_OrderBook_14to24july2026.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2955BEBB-AA89-402D-92BA-14DDAC2E3CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D73072-C491-40B4-B72B-F627F94574A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All_Backups" sheetId="2" r:id="rId1"/>
     <sheet name="For_Work" sheetId="3" r:id="rId2"/>
     <sheet name="Result" sheetId="4" r:id="rId3"/>
     <sheet name="Different_RoughCalculations" sheetId="5" r:id="rId4"/>
+    <sheet name="Rough" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">All_Backups!$B$1:$B$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">All_Backups!$B$1:$B$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">For_Work!$B$129:$B$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rough!$B$1:$B$245</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="606">
   <si>
     <t>Ord.Date &amp; Time</t>
   </si>
@@ -554,17 +556,1333 @@
   </si>
   <si>
     <t xml:space="preserve">nn </t>
+  </si>
+  <si>
+    <t>List Category</t>
+  </si>
+  <si>
+    <t>Stock Symbol</t>
+  </si>
+  <si>
+    <t>Sell Price (₹)</t>
+  </si>
+  <si>
+    <t>Sell Quantity</t>
+  </si>
+  <si>
+    <t>Corresponding Buy Data</t>
+  </si>
+  <si>
+    <t>Buy Date</t>
+  </si>
+  <si>
+    <t>1ST LIST</t>
+  </si>
+  <si>
+    <t>MOSCHIP</t>
+  </si>
+  <si>
+    <t>10*240</t>
+  </si>
+  <si>
+    <t>9/7/26</t>
+  </si>
+  <si>
+    <t>APOLLOTYRE</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>5*445</t>
+  </si>
+  <si>
+    <t>SILVERBEES</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>50*206</t>
+  </si>
+  <si>
+    <t>13/7/26</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>50*211</t>
+  </si>
+  <si>
+    <t>8/7/26</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>423.40</t>
+  </si>
+  <si>
+    <t>20@408.40</t>
+  </si>
+  <si>
+    <t>SOLARIND</t>
+  </si>
+  <si>
+    <t>18698</t>
+  </si>
+  <si>
+    <t>1@18052</t>
+  </si>
+  <si>
+    <t>7/7/26</t>
+  </si>
+  <si>
+    <t>IRFC</t>
+  </si>
+  <si>
+    <t>90.75</t>
+  </si>
+  <si>
+    <t>200*88.75</t>
+  </si>
+  <si>
+    <t>92.98</t>
+  </si>
+  <si>
+    <t>200@89.75</t>
+  </si>
+  <si>
+    <t>CGPOWER</t>
+  </si>
+  <si>
+    <t>948.60</t>
+  </si>
+  <si>
+    <t>35*906.51 (5 steps)</t>
+  </si>
+  <si>
+    <t>3/7/26</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>5*940+5*950+5*960</t>
+  </si>
+  <si>
+    <t>3,3,2/7/26</t>
+  </si>
+  <si>
+    <t>KERNEX</t>
+  </si>
+  <si>
+    <t>2264</t>
+  </si>
+  <si>
+    <t>1*2114+1*2014</t>
+  </si>
+  <si>
+    <t>8,8/7/26</t>
+  </si>
+  <si>
+    <t>2564</t>
+  </si>
+  <si>
+    <t>1*2264</t>
+  </si>
+  <si>
+    <t>2402.65</t>
+  </si>
+  <si>
+    <t>1*2106+1*1999.30</t>
+  </si>
+  <si>
+    <t>19,17/6/26</t>
+  </si>
+  <si>
+    <t>RVNL</t>
+  </si>
+  <si>
+    <t>238.20</t>
+  </si>
+  <si>
+    <t>70*227.14 IN 3 STEPS</t>
+  </si>
+  <si>
+    <t>IGIL</t>
+  </si>
+  <si>
+    <t>353.50</t>
+  </si>
+  <si>
+    <t>100@346.50</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>50@352</t>
+  </si>
+  <si>
+    <t>6/7/26</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>50@360</t>
+  </si>
+  <si>
+    <t>17/6/26</t>
+  </si>
+  <si>
+    <t>383, 392.50, 409</t>
+  </si>
+  <si>
+    <t>50@370, 20@360, 10+10@376.90+370</t>
+  </si>
+  <si>
+    <t>10,10june26, 2june26, 17Apr, 27may 2026</t>
+  </si>
+  <si>
+    <t>RAILTEL</t>
+  </si>
+  <si>
+    <t>319/314</t>
+  </si>
+  <si>
+    <t>50*306</t>
+  </si>
+  <si>
+    <t>10/7/26</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>30*309+30*315+30*312+30*321+30*318</t>
+  </si>
+  <si>
+    <t>6,1/7/26, 29,19/6/26</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>50@326</t>
+  </si>
+  <si>
+    <t>12 MAY 2026</t>
+  </si>
+  <si>
+    <t>VBL</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>10*482+10*492</t>
+  </si>
+  <si>
+    <t>7,6/7/26</t>
+  </si>
+  <si>
+    <t>533.40</t>
+  </si>
+  <si>
+    <t>10*516+20*506</t>
+  </si>
+  <si>
+    <t>22,22/6/26</t>
+  </si>
+  <si>
+    <t>557.50</t>
+  </si>
+  <si>
+    <t>10+10@515+530</t>
+  </si>
+  <si>
+    <t>9,3 june 2026</t>
+  </si>
+  <si>
+    <t>BDL</t>
+  </si>
+  <si>
+    <t>1428</t>
+  </si>
+  <si>
+    <t>10*1363</t>
+  </si>
+  <si>
+    <t>1466</t>
+  </si>
+  <si>
+    <t>10*1401</t>
+  </si>
+  <si>
+    <t>11 MAY 2026</t>
+  </si>
+  <si>
+    <t>1698.80</t>
+  </si>
+  <si>
+    <t>2*1373.80</t>
+  </si>
+  <si>
+    <t>20 Apr 2026</t>
+  </si>
+  <si>
+    <t>COCHINSHIP</t>
+  </si>
+  <si>
+    <t>1574, 1708.50</t>
+  </si>
+  <si>
+    <t>5+5@1526+1476, 10@1638.50 (in 2 steps)</t>
+  </si>
+  <si>
+    <t>18may26, 12 May 2026</t>
+  </si>
+  <si>
+    <t>NETWEB</t>
+  </si>
+  <si>
+    <t>5411</t>
+  </si>
+  <si>
+    <t>1*5108+1*5014</t>
+  </si>
+  <si>
+    <t>19&amp;18/6/26</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>3341.50</t>
+  </si>
+  <si>
+    <t>2*3047(in 2 steps)+1*3179.50</t>
+  </si>
+  <si>
+    <t>7/7,18/6/26</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
+  </si>
+  <si>
+    <t>1334.50</t>
+  </si>
+  <si>
+    <t>1*1102+2*1090.70</t>
+  </si>
+  <si>
+    <t>8/7,18/6/26</t>
+  </si>
+  <si>
+    <t>SCI</t>
+  </si>
+  <si>
+    <t>320.50</t>
+  </si>
+  <si>
+    <t>10*301+10*290+10*301+10*310</t>
+  </si>
+  <si>
+    <t>1july,10JUNE,25,25 MAY 2026</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>10+10@330+320</t>
+  </si>
+  <si>
+    <t>12,22 MAY 2026</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>4048</t>
+  </si>
+  <si>
+    <t>10*3912.20 (IN 4 STEPS)</t>
+  </si>
+  <si>
+    <t>4129</t>
+  </si>
+  <si>
+    <t>2*4002+3*3980</t>
+  </si>
+  <si>
+    <t>7,7/7/26</t>
+  </si>
+  <si>
+    <t>4177</t>
+  </si>
+  <si>
+    <t>2*4002+3*4023</t>
+  </si>
+  <si>
+    <t>2,2/7/26</t>
+  </si>
+  <si>
+    <t>MCX</t>
+  </si>
+  <si>
+    <t>2847</t>
+  </si>
+  <si>
+    <t>4@2646.50 IN 2 STEPS</t>
+  </si>
+  <si>
+    <t>3365</t>
+  </si>
+  <si>
+    <t>1*3200+1*2830</t>
+  </si>
+  <si>
+    <t>5 JUNE, 12 MAY 2026</t>
+  </si>
+  <si>
+    <t>INDHOTEL</t>
+  </si>
+  <si>
+    <t>772</t>
+  </si>
+  <si>
+    <t>5*712+5*722.80+5*730</t>
+  </si>
+  <si>
+    <t>23,19/6/26</t>
+  </si>
+  <si>
+    <t>HDFCAMC</t>
+  </si>
+  <si>
+    <t>2908.90</t>
+  </si>
+  <si>
+    <t>5@ 2778.90</t>
+  </si>
+  <si>
+    <t>17 Apr 2026</t>
+  </si>
+  <si>
+    <t>EASEMYTRIP</t>
+  </si>
+  <si>
+    <t>9.33</t>
+  </si>
+  <si>
+    <t>1000 @ 8.68 + 500 @ 7.94</t>
+  </si>
+  <si>
+    <t>24 Feb 2026 + 2 Mar 2026</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>4584 (OR 5@4590, 5@4690)</t>
+  </si>
+  <si>
+    <t>5+5@4460+4560</t>
+  </si>
+  <si>
+    <t>15may26</t>
+  </si>
+  <si>
+    <t>4760</t>
+  </si>
+  <si>
+    <t>5@4630</t>
+  </si>
+  <si>
+    <t>ITBEES</t>
+  </si>
+  <si>
+    <t>37.01</t>
+  </si>
+  <si>
+    <t>200 @ 33.51</t>
+  </si>
+  <si>
+    <t>24/2/26</t>
+  </si>
+  <si>
+    <t>GTD LIST</t>
+  </si>
+  <si>
+    <t>428.20</t>
+  </si>
+  <si>
+    <t>50@415.20</t>
+  </si>
+  <si>
+    <t>GOLDBEES</t>
+  </si>
+  <si>
+    <t>125.20</t>
+  </si>
+  <si>
+    <t>100@118.70 + 50@115.26</t>
+  </si>
+  <si>
+    <t>19/6/26 + 25/6/26</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>20*296+20*286+20*276</t>
+  </si>
+  <si>
+    <t>6,8,8/7/26</t>
+  </si>
+  <si>
+    <t>4614</t>
+  </si>
+  <si>
+    <t>1*4314</t>
+  </si>
+  <si>
+    <t>4960</t>
+  </si>
+  <si>
+    <t>1*4914+1*4714+1*4514</t>
+  </si>
+  <si>
+    <t>29/6/26</t>
+  </si>
+  <si>
+    <t>ZENTEC</t>
+  </si>
+  <si>
+    <t>1934</t>
+  </si>
+  <si>
+    <t>5*1814+5*1914</t>
+  </si>
+  <si>
+    <t>24,23/6/26</t>
+  </si>
+  <si>
+    <t>BSE</t>
+  </si>
+  <si>
+    <t>3938</t>
+  </si>
+  <si>
+    <t>2*3664+1*3764</t>
+  </si>
+  <si>
+    <t>4114.25</t>
+  </si>
+  <si>
+    <t>1*3864+1*3863+1*3963+1*3916.90</t>
+  </si>
+  <si>
+    <t>25,3,2june, 8MAY 26</t>
+  </si>
+  <si>
+    <t>4895</t>
+  </si>
+  <si>
+    <t>1@4245</t>
+  </si>
+  <si>
+    <t>27 MAY 2026</t>
+  </si>
+  <si>
+    <t>PRINCEPIPE</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>20*261+20*266+20*271</t>
+  </si>
+  <si>
+    <t>8,8,7/7/26</t>
+  </si>
+  <si>
+    <t>298.50</t>
+  </si>
+  <si>
+    <t>20*280+20*281</t>
+  </si>
+  <si>
+    <t>25/6/26</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>5@290</t>
+  </si>
+  <si>
+    <t>20 MAY 2026</t>
+  </si>
+  <si>
+    <t>128.50</t>
+  </si>
+  <si>
+    <t>50*121+50*122</t>
+  </si>
+  <si>
+    <t>10,18June2026</t>
+  </si>
+  <si>
+    <t>19220</t>
+  </si>
+  <si>
+    <t>1@18570</t>
+  </si>
+  <si>
+    <t>27/5/26</t>
+  </si>
+  <si>
+    <t>IRCON</t>
+  </si>
+  <si>
+    <t>150.27</t>
+  </si>
+  <si>
+    <t>100@143.77</t>
+  </si>
+  <si>
+    <t>15 MAY 2026</t>
+  </si>
+  <si>
+    <t>222.55</t>
+  </si>
+  <si>
+    <t>50*216+100*216.05</t>
+  </si>
+  <si>
+    <t>7/7/26, 23/6/26</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>50@252</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>30*234+30*237+30*241+30*244</t>
+  </si>
+  <si>
+    <t>6/7/26; 24,23,19/6/26</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>20+50@234.58+245</t>
+  </si>
+  <si>
+    <t>2june, 29 MAY 2026</t>
+  </si>
+  <si>
+    <t>297.50</t>
+  </si>
+  <si>
+    <t>50 @ 284.50</t>
+  </si>
+  <si>
+    <t>13 May 2026</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>50 @ 292</t>
+  </si>
+  <si>
+    <t>12 May 2026</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>50 @ 296</t>
+  </si>
+  <si>
+    <t>11 May 2026</t>
+  </si>
+  <si>
+    <t>314.80</t>
+  </si>
+  <si>
+    <t>50 @ 300.80 (IN 2 STEPS)</t>
+  </si>
+  <si>
+    <t>2 Mar 2026</t>
+  </si>
+  <si>
+    <t>WAAREERTL</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>25 @ 1050</t>
+  </si>
+  <si>
+    <t>24 APR 2026</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>50 @ 1070</t>
+  </si>
+  <si>
+    <t>GRSE</t>
+  </si>
+  <si>
+    <t>2896</t>
+  </si>
+  <si>
+    <t>5*2790+5*2860.60</t>
+  </si>
+  <si>
+    <t>2908</t>
+  </si>
+  <si>
+    <t>5+5@ 2863+2813</t>
+  </si>
+  <si>
+    <t>12 may 2026</t>
+  </si>
+  <si>
+    <t>3059</t>
+  </si>
+  <si>
+    <t>5+5@ 2963+3010</t>
+  </si>
+  <si>
+    <t>11 may 2026</t>
+  </si>
+  <si>
+    <t>34.86</t>
+  </si>
+  <si>
+    <t>500 @ 33.36</t>
+  </si>
+  <si>
+    <t>23 APR 2026</t>
+  </si>
+  <si>
+    <t>HINDUNI</t>
+  </si>
+  <si>
+    <t>2284</t>
+  </si>
+  <si>
+    <t>5@2154</t>
+  </si>
+  <si>
+    <t>11june 2026</t>
+  </si>
+  <si>
+    <t>4245</t>
+  </si>
+  <si>
+    <t>2*4086+2*4126+3*4156+3*4186</t>
+  </si>
+  <si>
+    <t>7,7/1/26, 30,24/6/26</t>
+  </si>
+  <si>
+    <t>3RD LIST (DISTANT)</t>
+  </si>
+  <si>
+    <t>1843</t>
+  </si>
+  <si>
+    <t>5@1713</t>
+  </si>
+  <si>
+    <t>1969</t>
+  </si>
+  <si>
+    <t>3@1752</t>
+  </si>
+  <si>
+    <t>29 APR 2026</t>
+  </si>
+  <si>
+    <t>MAZDOCK</t>
+  </si>
+  <si>
+    <t>3353.70</t>
+  </si>
+  <si>
+    <t>1@2753.70</t>
+  </si>
+  <si>
+    <t>4530</t>
+  </si>
+  <si>
+    <t>3 @ 4,296.00</t>
+  </si>
+  <si>
+    <t>24 Feb 2026</t>
+  </si>
+  <si>
+    <t>IREDA</t>
+  </si>
+  <si>
+    <t>147.50</t>
+  </si>
+  <si>
+    <t>50@134.50</t>
+  </si>
+  <si>
+    <t>30apr2026</t>
+  </si>
+  <si>
+    <t>172.50</t>
+  </si>
+  <si>
+    <t>10 @ 138.60 + 10@135.93</t>
+  </si>
+  <si>
+    <t>22 APR 2026</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>15@1061.10</t>
+  </si>
+  <si>
+    <t>8may2026</t>
+  </si>
+  <si>
+    <t>1320</t>
+  </si>
+  <si>
+    <t>5@ 1189.90</t>
+  </si>
+  <si>
+    <t>1409</t>
+  </si>
+  <si>
+    <t>3@ 1203.90</t>
+  </si>
+  <si>
+    <t>25 Feb 2026</t>
+  </si>
+  <si>
+    <t>2ND LIST (ALREADY SOLD)</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>50 @ 1082</t>
+  </si>
+  <si>
+    <t>20 APR 2026</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>30 @ 1102</t>
+  </si>
+  <si>
+    <t>17 APR 2026</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>20 @ 1151</t>
+  </si>
+  <si>
+    <t>3043</t>
+  </si>
+  <si>
+    <t>5@ 2913</t>
+  </si>
+  <si>
+    <t>3192</t>
+  </si>
+  <si>
+    <t>10+2@ 3122+3106</t>
+  </si>
+  <si>
+    <t>29 Apr 2026</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>2+2 @ 3294.60+3206</t>
+  </si>
+  <si>
+    <t>1901.08</t>
+  </si>
+  <si>
+    <t>2@ 1805 + 3@1731.80 + 3@1666</t>
+  </si>
+  <si>
+    <t>21 Apr 2026 + 23 APR 2026 + 24 APR 2026</t>
+  </si>
+  <si>
+    <t>NAM-INDIA</t>
+  </si>
+  <si>
+    <t>933.50</t>
+  </si>
+  <si>
+    <t>20@ 898.50 (in 2 steps)</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>30 @ 946 (IN 3 STEPS)</t>
+  </si>
+  <si>
+    <t>26 Feb 2026</t>
+  </si>
+  <si>
+    <t>989.90</t>
+  </si>
+  <si>
+    <t>9@924.90</t>
+  </si>
+  <si>
+    <t>13 APR 2026</t>
+  </si>
+  <si>
+    <t>Buy Price (₹)</t>
+  </si>
+  <si>
+    <t>Buy Quantity</t>
+  </si>
+  <si>
+    <t>Corresponding Sell Data</t>
+  </si>
+  <si>
+    <t>Sell Date</t>
+  </si>
+  <si>
+    <t>31.01</t>
+  </si>
+  <si>
+    <t>200 @ 32.51</t>
+  </si>
+  <si>
+    <t>17/7/26</t>
+  </si>
+  <si>
+    <t>1415</t>
+  </si>
+  <si>
+    <t>15@1495</t>
+  </si>
+  <si>
+    <t>2702 / 2651</t>
+  </si>
+  <si>
+    <t>11@2748</t>
+  </si>
+  <si>
+    <t>SENCO</t>
+  </si>
+  <si>
+    <t>345.35/352</t>
+  </si>
+  <si>
+    <t>25@365.35</t>
+  </si>
+  <si>
+    <t>335</t>
+  </si>
+  <si>
+    <t>25@348</t>
+  </si>
+  <si>
+    <t>JUSTDIAL</t>
+  </si>
+  <si>
+    <t>561.95</t>
+  </si>
+  <si>
+    <t>50*601.95 (IN 2 STEPS)</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>25@566</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>25@558</t>
+  </si>
+  <si>
+    <t>537</t>
+  </si>
+  <si>
+    <t>25@549</t>
+  </si>
+  <si>
+    <t>530</t>
+  </si>
+  <si>
+    <t>25@541</t>
+  </si>
+  <si>
+    <t>KFINTECH</t>
+  </si>
+  <si>
+    <t>897</t>
+  </si>
+  <si>
+    <t>20*917+10*927</t>
+  </si>
+  <si>
+    <t>13,13/7/26</t>
+  </si>
+  <si>
+    <t>877</t>
+  </si>
+  <si>
+    <t>10@907</t>
+  </si>
+  <si>
+    <t>10,9/7/26</t>
+  </si>
+  <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>40@882 (IN 4 STEPS)</t>
+  </si>
+  <si>
+    <t>EXIDEINDIA</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>29@420.60</t>
+  </si>
+  <si>
+    <t>2/7/26</t>
+  </si>
+  <si>
+    <t>CDSL</t>
+  </si>
+  <si>
+    <t>1267</t>
+  </si>
+  <si>
+    <t>69@1297</t>
+  </si>
+  <si>
+    <t>18/6/26</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>30@1031</t>
+  </si>
+  <si>
+    <t>15june26</t>
+  </si>
+  <si>
+    <t>2805</t>
+  </si>
+  <si>
+    <t>10@2895</t>
+  </si>
+  <si>
+    <t>665.95</t>
+  </si>
+  <si>
+    <t>90@674.95</t>
+  </si>
+  <si>
+    <t>12june26</t>
+  </si>
+  <si>
+    <t>656</t>
+  </si>
+  <si>
+    <t>90@665</t>
+  </si>
+  <si>
+    <t>DIXON</t>
+  </si>
+  <si>
+    <t>11680</t>
+  </si>
+  <si>
+    <t>1@12330</t>
+  </si>
+  <si>
+    <t>11075, 10575</t>
+  </si>
+  <si>
+    <t>2@11400, 2@10900</t>
+  </si>
+  <si>
+    <t>22, 20 MAY 2026</t>
+  </si>
+  <si>
+    <t>331, 327, 322</t>
+  </si>
+  <si>
+    <t>100@348.50, 100@344, 100@338</t>
+  </si>
+  <si>
+    <t>20may2026</t>
+  </si>
+  <si>
+    <t>334, 329</t>
+  </si>
+  <si>
+    <t>100@334, 100@329</t>
+  </si>
+  <si>
+    <t>19 MAY 2026</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>40*229+40*219</t>
+  </si>
+  <si>
+    <t>6,3/7/26</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>100@214</t>
+  </si>
+  <si>
+    <t>183.70</t>
+  </si>
+  <si>
+    <t>100@190.20</t>
+  </si>
+  <si>
+    <t>16/4/26</t>
+  </si>
+  <si>
+    <t>264.70</t>
+  </si>
+  <si>
+    <t>37 @ 284.70</t>
+  </si>
+  <si>
+    <t>16 APR 2026</t>
+  </si>
+  <si>
+    <t>1793</t>
+  </si>
+  <si>
+    <t>3@1998</t>
+  </si>
+  <si>
+    <t>12june2026</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>25 @ 1048</t>
+  </si>
+  <si>
+    <t>7 APR 2026</t>
+  </si>
+  <si>
+    <t>1510, 1395</t>
+  </si>
+  <si>
+    <t>10@1610, 30@1420</t>
+  </si>
+  <si>
+    <t>20may26, 7 APR 2026</t>
+  </si>
+  <si>
+    <t>709</t>
+  </si>
+  <si>
+    <t>14@ 749</t>
+  </si>
+  <si>
+    <t>15 APR 2026</t>
+  </si>
+  <si>
+    <t>705</t>
+  </si>
+  <si>
+    <t>50 @ 719</t>
+  </si>
+  <si>
+    <t>8 Feb 2026</t>
+  </si>
+  <si>
+    <t>652</t>
+  </si>
+  <si>
+    <t>100 @ 666</t>
+  </si>
+  <si>
+    <t>3 Feb 2026</t>
+  </si>
+  <si>
+    <t>2583, 2552</t>
+  </si>
+  <si>
+    <t>10@2696, 10@2680, 10@2648, 10@2617</t>
+  </si>
+  <si>
+    <t>15,15,12,12june26</t>
+  </si>
+  <si>
+    <t>2460</t>
+  </si>
+  <si>
+    <t>30 @ 2490</t>
+  </si>
+  <si>
+    <t>2435</t>
+  </si>
+  <si>
+    <t>30 @ 2465</t>
+  </si>
+  <si>
+    <t>8 APR 2026</t>
+  </si>
+  <si>
+    <t>5@ 2935</t>
+  </si>
+  <si>
+    <t>17 MAR 2026</t>
+  </si>
+  <si>
+    <t>300.10</t>
+  </si>
+  <si>
+    <t>100@299 + 100@309</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>912</t>
+  </si>
+  <si>
+    <t>10 @ 957</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>9 @ 950</t>
+  </si>
+  <si>
+    <t>10 APR 2026</t>
+  </si>
+  <si>
+    <t>890</t>
+  </si>
+  <si>
+    <t>60 @ 904</t>
+  </si>
+  <si>
+    <t>9 APR 2026</t>
+  </si>
+  <si>
+    <t>14585</t>
+  </si>
+  <si>
+    <t>2@14915</t>
+  </si>
+  <si>
+    <t>13775</t>
+  </si>
+  <si>
+    <t>2@14100</t>
+  </si>
+  <si>
+    <t>13660</t>
+  </si>
+  <si>
+    <t>2 @ 13990</t>
+  </si>
+  <si>
+    <t>4159</t>
+  </si>
+  <si>
+    <t>20@ 4219</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>30 @ 2530</t>
+  </si>
+  <si>
+    <t>2152</t>
+  </si>
+  <si>
+    <t>50 @ 2180</t>
+  </si>
+  <si>
+    <t>2030</t>
+  </si>
+  <si>
+    <t>50 @ 2044.95</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -572,8 +1890,17 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -658,8 +1985,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5597"/>
+        <bgColor rgb="FF2F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F9"/>
+        <bgColor rgb="FFF2F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F1E6"/>
+        <bgColor rgb="FFE9F1E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+        <bgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+        <bgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -736,13 +2105,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -773,7 +2159,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -800,7 +2186,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -810,18 +2196,116 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="16" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="18" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="19" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="20" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="21" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{4C069254-30C5-44EC-835A-DFFFBC861B1B}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{68514157-655D-4D47-ACE7-0EB494B7424D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -1123,6 +2607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G155"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1153,7 +2638,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1173,7 +2658,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1193,7 +2678,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1213,7 +2698,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -1233,7 +2718,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>1</v>
       </c>
@@ -1253,7 +2738,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>1</v>
       </c>
@@ -1273,7 +2758,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>1</v>
       </c>
@@ -1293,7 +2778,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>1</v>
       </c>
@@ -1313,7 +2798,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>1</v>
       </c>
@@ -1333,7 +2818,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>1</v>
       </c>
@@ -1353,7 +2838,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>1</v>
       </c>
@@ -1373,7 +2858,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
@@ -1393,7 +2878,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>1</v>
       </c>
@@ -1413,7 +2898,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>1</v>
       </c>
@@ -1433,7 +2918,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>1</v>
       </c>
@@ -1453,7 +2938,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>1</v>
       </c>
@@ -1473,7 +2958,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>1</v>
       </c>
@@ -1493,7 +2978,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1501,7 +2986,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -1521,7 +3006,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>63</v>
       </c>
@@ -1541,7 +3026,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>64</v>
       </c>
@@ -1561,7 +3046,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>67</v>
       </c>
@@ -1581,7 +3066,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>69</v>
       </c>
@@ -1601,7 +3086,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>71</v>
       </c>
@@ -1621,7 +3106,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>72</v>
       </c>
@@ -1641,7 +3126,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>73</v>
       </c>
@@ -1661,7 +3146,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
@@ -1681,7 +3166,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>75</v>
       </c>
@@ -1701,7 +3186,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>77</v>
       </c>
@@ -1721,7 +3206,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>79</v>
       </c>
@@ -1741,7 +3226,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>80</v>
       </c>
@@ -1761,7 +3246,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>81</v>
       </c>
@@ -1781,7 +3266,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>82</v>
       </c>
@@ -1801,7 +3286,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>83</v>
       </c>
@@ -1821,7 +3306,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>84</v>
       </c>
@@ -1841,7 +3326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>83</v>
       </c>
@@ -1861,7 +3346,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>83</v>
       </c>
@@ -1881,7 +3366,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>83</v>
       </c>
@@ -1901,7 +3386,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="7" t="s">
         <v>85</v>
       </c>
@@ -1921,7 +3406,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1932,7 +3417,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>86</v>
       </c>
@@ -1955,7 +3440,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>87</v>
       </c>
@@ -1978,7 +3463,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>88</v>
       </c>
@@ -2001,7 +3486,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>89</v>
       </c>
@@ -2024,7 +3509,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>90</v>
       </c>
@@ -2070,7 +3555,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>92</v>
       </c>
@@ -2093,7 +3578,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>90</v>
       </c>
@@ -2116,7 +3601,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>93</v>
       </c>
@@ -2139,7 +3624,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>94</v>
       </c>
@@ -2162,7 +3647,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>94</v>
       </c>
@@ -2185,7 +3670,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>93</v>
       </c>
@@ -2208,7 +3693,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>94</v>
       </c>
@@ -2231,7 +3716,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>94</v>
       </c>
@@ -2254,7 +3739,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>95</v>
       </c>
@@ -2277,7 +3762,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>96</v>
       </c>
@@ -2300,7 +3785,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
@@ -2323,7 +3808,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>97</v>
       </c>
@@ -2346,7 +3831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>97</v>
       </c>
@@ -2369,7 +3854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>97</v>
       </c>
@@ -2392,7 +3877,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>97</v>
       </c>
@@ -2415,7 +3900,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>97</v>
       </c>
@@ -2461,7 +3946,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>97</v>
       </c>
@@ -2484,7 +3969,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>97</v>
       </c>
@@ -2507,7 +3992,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>97</v>
       </c>
@@ -2530,7 +4015,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>97</v>
       </c>
@@ -2553,7 +4038,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
@@ -2576,7 +4061,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>108</v>
       </c>
@@ -2622,7 +4107,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>110</v>
       </c>
@@ -2645,7 +4130,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>110</v>
       </c>
@@ -2668,7 +4153,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
         <v>111</v>
       </c>
@@ -2691,7 +4176,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
         <v>112</v>
       </c>
@@ -2714,7 +4199,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
         <v>113</v>
       </c>
@@ -2737,7 +4222,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
         <v>111</v>
       </c>
@@ -2760,7 +4245,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
         <v>114</v>
       </c>
@@ -2783,7 +4268,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="7" t="s">
         <v>114</v>
       </c>
@@ -2806,7 +4291,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
         <v>0</v>
       </c>
@@ -2829,7 +4314,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2" t="s">
         <v>115</v>
       </c>
@@ -2852,7 +4337,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="4" t="s">
         <v>115</v>
       </c>
@@ -2875,7 +4360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="4" t="s">
         <v>115</v>
       </c>
@@ -2898,7 +4383,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="4" t="s">
         <v>115</v>
       </c>
@@ -2921,7 +4406,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="4" t="s">
         <v>115</v>
       </c>
@@ -2944,7 +4429,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="4" t="s">
         <v>115</v>
       </c>
@@ -2967,7 +4452,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="4" t="s">
         <v>115</v>
       </c>
@@ -2990,7 +4475,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
         <v>0</v>
       </c>
@@ -3036,7 +4521,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>123</v>
       </c>
@@ -3059,7 +4544,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>123</v>
       </c>
@@ -3082,7 +4567,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>123</v>
       </c>
@@ -3105,7 +4590,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>123</v>
       </c>
@@ -3128,7 +4613,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>123</v>
       </c>
@@ -3151,7 +4636,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>123</v>
       </c>
@@ -3174,7 +4659,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>123</v>
       </c>
@@ -3197,7 +4682,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>123</v>
       </c>
@@ -3220,7 +4705,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>123</v>
       </c>
@@ -3243,7 +4728,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>123</v>
       </c>
@@ -3266,7 +4751,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>123</v>
       </c>
@@ -3289,7 +4774,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>123</v>
       </c>
@@ -3312,7 +4797,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>123</v>
       </c>
@@ -3335,7 +4820,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>123</v>
       </c>
@@ -3358,7 +4843,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>123</v>
       </c>
@@ -3381,7 +4866,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>123</v>
       </c>
@@ -3404,7 +4889,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>123</v>
       </c>
@@ -3427,7 +4912,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>123</v>
       </c>
@@ -3450,7 +4935,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>123</v>
       </c>
@@ -3473,7 +4958,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
         <v>0</v>
       </c>
@@ -3496,7 +4981,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>140</v>
       </c>
@@ -3519,7 +5004,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>141</v>
       </c>
@@ -3542,7 +5027,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>142</v>
       </c>
@@ -3565,7 +5050,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>143</v>
       </c>
@@ -3611,7 +5096,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>145</v>
       </c>
@@ -3634,7 +5119,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>146</v>
       </c>
@@ -3726,7 +5211,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>147</v>
       </c>
@@ -3749,7 +5234,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>149</v>
       </c>
@@ -3772,7 +5257,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>147</v>
       </c>
@@ -3795,7 +5280,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>150</v>
       </c>
@@ -3818,7 +5303,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>150</v>
       </c>
@@ -3841,7 +5326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>147</v>
       </c>
@@ -3864,7 +5349,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>147</v>
       </c>
@@ -3887,7 +5372,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>150</v>
       </c>
@@ -3910,7 +5395,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>147</v>
       </c>
@@ -3933,7 +5418,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>151</v>
       </c>
@@ -3956,7 +5441,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>152</v>
       </c>
@@ -3979,7 +5464,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:7" ht="15.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -4002,7 +5487,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>157</v>
       </c>
@@ -4025,7 +5510,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>158</v>
       </c>
@@ -4048,7 +5533,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>159</v>
       </c>
@@ -4071,7 +5556,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>160</v>
       </c>
@@ -4094,7 +5579,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>161</v>
       </c>
@@ -4117,7 +5602,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>162</v>
       </c>
@@ -4140,7 +5625,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>162</v>
       </c>
@@ -4163,7 +5648,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>162</v>
       </c>
@@ -4186,7 +5671,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>162</v>
       </c>
@@ -4209,7 +5694,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>162</v>
       </c>
@@ -4232,7 +5717,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>162</v>
       </c>
@@ -4255,7 +5740,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>162</v>
       </c>
@@ -4278,7 +5763,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>166</v>
       </c>
@@ -4301,7 +5786,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>166</v>
       </c>
@@ -4324,7 +5809,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>167</v>
       </c>
@@ -4347,7 +5832,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>168</v>
       </c>
@@ -4370,7 +5855,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>168</v>
       </c>
@@ -4393,7 +5878,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>168</v>
       </c>
@@ -4416,7 +5901,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>169</v>
       </c>
@@ -4439,7 +5924,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>166</v>
       </c>
@@ -4462,7 +5947,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>166</v>
       </c>
@@ -4485,7 +5970,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>168</v>
       </c>
@@ -4508,7 +5993,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>166</v>
       </c>
@@ -4531,7 +6016,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>168</v>
       </c>
@@ -4555,6 +6040,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B155" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="WAAREERTLEQ"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10062,4 +11554,4587 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDEAB589-59D4-402D-A28C-AA7262E65C2C}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G245"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4">
+        <v>881</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5">
+        <v>5</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>891</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4">
+        <v>871</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="5">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4">
+        <v>417.25</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>3564</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>7220</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="5">
+        <v>5</v>
+      </c>
+      <c r="F14" s="4">
+        <v>421</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="5">
+        <v>100</v>
+      </c>
+      <c r="E15" s="5">
+        <v>100</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="5">
+        <v>200</v>
+      </c>
+      <c r="E16" s="5">
+        <v>200</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="5">
+        <v>5</v>
+      </c>
+      <c r="E19" s="5">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4">
+        <v>702</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3</v>
+      </c>
+      <c r="E22" s="5">
+        <v>3</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="5">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1326</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="5">
+        <v>5</v>
+      </c>
+      <c r="E25" s="5">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="5">
+        <v>10</v>
+      </c>
+      <c r="E26" s="5">
+        <v>10</v>
+      </c>
+      <c r="F26" s="4">
+        <v>882</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="5">
+        <v>5</v>
+      </c>
+      <c r="E27" s="5">
+        <v>5</v>
+      </c>
+      <c r="F27" s="4">
+        <v>892</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="6">
+        <v>10</v>
+      </c>
+      <c r="E28" s="6">
+        <v>10</v>
+      </c>
+      <c r="F28" s="4">
+        <v>852</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="6">
+        <v>5</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5</v>
+      </c>
+      <c r="F29" s="4">
+        <v>862</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="6">
+        <v>5</v>
+      </c>
+      <c r="E30" s="6">
+        <v>5</v>
+      </c>
+      <c r="F30" s="4">
+        <v>872</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="5">
+        <v>10</v>
+      </c>
+      <c r="E32" s="5">
+        <v>10</v>
+      </c>
+      <c r="F32" s="4">
+        <v>2583</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="5">
+        <v>10</v>
+      </c>
+      <c r="E33" s="5">
+        <v>10</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2572</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="6">
+        <v>5</v>
+      </c>
+      <c r="E34" s="6">
+        <v>5</v>
+      </c>
+      <c r="F34" s="4">
+        <v>2546</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="5">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5">
+        <v>15</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="5">
+        <v>2</v>
+      </c>
+      <c r="E37" s="5">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="5">
+        <v>11</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" s="5">
+        <v>3</v>
+      </c>
+      <c r="E40" s="5">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4">
+        <v>2610</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="5">
+        <v>2</v>
+      </c>
+      <c r="E41" s="5">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="5">
+        <v>100</v>
+      </c>
+      <c r="E43" s="5">
+        <v>100</v>
+      </c>
+      <c r="F43" s="4">
+        <v>334</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="5">
+        <v>100</v>
+      </c>
+      <c r="E44" s="5">
+        <v>100</v>
+      </c>
+      <c r="F44" s="4">
+        <v>331</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="5">
+        <v>30</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="8">
+        <v>10</v>
+      </c>
+      <c r="F47" s="7">
+        <v>907</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48" s="5">
+        <v>20</v>
+      </c>
+      <c r="E48" s="5">
+        <v>20</v>
+      </c>
+      <c r="F48" s="4">
+        <v>887</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="5">
+        <v>10</v>
+      </c>
+      <c r="E49" s="5">
+        <v>10</v>
+      </c>
+      <c r="F49" s="4">
+        <v>870</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" s="5">
+        <v>40</v>
+      </c>
+      <c r="E50" s="5">
+        <v>40</v>
+      </c>
+      <c r="F50" s="4">
+        <v>862</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="29"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="28"/>
+    </row>
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="5">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2</v>
+      </c>
+      <c r="F53" s="4">
+        <v>3803</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="5">
+        <v>3</v>
+      </c>
+      <c r="F54" s="4">
+        <v>3826</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="5">
+        <v>2</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2</v>
+      </c>
+      <c r="F55" s="4">
+        <v>3726</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" s="5">
+        <v>2</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2</v>
+      </c>
+      <c r="F56" s="4">
+        <v>3756</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="3">
+        <v>4</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" s="5">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="5">
+        <v>5</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" s="8">
+        <v>5</v>
+      </c>
+      <c r="E62" s="8">
+        <v>5</v>
+      </c>
+      <c r="F62" s="7">
+        <v>1171</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="5">
+        <v>5</v>
+      </c>
+      <c r="E63" s="5">
+        <v>5</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="5">
+        <v>5</v>
+      </c>
+      <c r="E64" s="5">
+        <v>5</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" s="5">
+        <v>5</v>
+      </c>
+      <c r="E65" s="5">
+        <v>5</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66" s="5">
+        <v>5</v>
+      </c>
+      <c r="E66" s="5">
+        <v>5</v>
+      </c>
+      <c r="F66" s="4">
+        <v>1101</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D67" s="5">
+        <v>5</v>
+      </c>
+      <c r="E67" s="5">
+        <v>5</v>
+      </c>
+      <c r="F67" s="4">
+        <v>1111</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D68" s="5">
+        <v>5</v>
+      </c>
+      <c r="E68" s="5">
+        <v>5</v>
+      </c>
+      <c r="F68" s="4">
+        <v>1121</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D69" s="5">
+        <v>5</v>
+      </c>
+      <c r="E69" s="5">
+        <v>5</v>
+      </c>
+      <c r="F69" s="4">
+        <v>1131</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D70" s="5">
+        <v>5</v>
+      </c>
+      <c r="E70" s="5">
+        <v>5</v>
+      </c>
+      <c r="F70" s="4">
+        <v>1080</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="5"/>
+    </row>
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D72" s="5">
+        <v>1</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4">
+        <v>4164</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" s="5">
+        <v>2</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D75" s="5">
+        <v>50</v>
+      </c>
+      <c r="E75" s="5">
+        <v>50</v>
+      </c>
+      <c r="F75" s="4">
+        <v>301</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" s="6">
+        <v>50</v>
+      </c>
+      <c r="E76" s="6">
+        <v>50</v>
+      </c>
+      <c r="F76" s="4">
+        <v>296</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="5">
+        <v>50</v>
+      </c>
+      <c r="E77" s="5">
+        <v>50</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D78" s="5">
+        <v>10</v>
+      </c>
+      <c r="E78" s="5">
+        <v>10</v>
+      </c>
+      <c r="F78" s="4">
+        <v>280.7</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D79" s="5">
+        <v>10</v>
+      </c>
+      <c r="E79" s="5">
+        <v>10</v>
+      </c>
+      <c r="F79" s="4">
+        <v>286</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" s="5">
+        <v>30</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" s="5">
+        <v>30</v>
+      </c>
+      <c r="E82" s="5">
+        <v>30</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D84" s="5">
+        <v>5</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" s="5">
+        <v>50</v>
+      </c>
+      <c r="E85" s="5">
+        <v>50</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86" s="5">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4">
+        <v>18698</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D88" s="5">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" s="5">
+        <v>2</v>
+      </c>
+      <c r="E89" s="5">
+        <v>2</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D90" s="5">
+        <v>5</v>
+      </c>
+      <c r="E90" s="5">
+        <v>5</v>
+      </c>
+      <c r="F90" s="4">
+        <v>3862</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="4"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="5"/>
+    </row>
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D93" s="5">
+        <v>5</v>
+      </c>
+      <c r="E93" s="5">
+        <v>5</v>
+      </c>
+      <c r="F93" s="4">
+        <v>952</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D94" s="5">
+        <v>5</v>
+      </c>
+      <c r="E94" s="5">
+        <v>5</v>
+      </c>
+      <c r="F94" s="4">
+        <v>936</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D96" s="6">
+        <v>10</v>
+      </c>
+      <c r="E96" s="6">
+        <v>10</v>
+      </c>
+      <c r="F96" s="4">
+        <v>516.70000000000005</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D97" s="5">
+        <v>10</v>
+      </c>
+      <c r="E97" s="5">
+        <v>10</v>
+      </c>
+      <c r="F97" s="4">
+        <v>226</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D98" s="5">
+        <v>37</v>
+      </c>
+      <c r="E98" s="5">
+        <v>37</v>
+      </c>
+      <c r="F98" s="4">
+        <v>264.7</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D99" s="5">
+        <v>10</v>
+      </c>
+      <c r="E99" s="5">
+        <v>10</v>
+      </c>
+      <c r="F99" s="4">
+        <v>2840</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="101" spans="1:7" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="B101" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E101" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C102" s="33">
+        <v>270</v>
+      </c>
+      <c r="D102" s="34">
+        <v>10</v>
+      </c>
+      <c r="E102" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="F102" s="35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B103" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C103" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="D103" s="34">
+        <v>5</v>
+      </c>
+      <c r="E103" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="F103" s="35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B104" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C104" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D104" s="34">
+        <v>50</v>
+      </c>
+      <c r="E104" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="F104" s="35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B105" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C105" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="D105" s="34">
+        <v>50</v>
+      </c>
+      <c r="E105" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="F105" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C106" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D106" s="34">
+        <v>20</v>
+      </c>
+      <c r="E106" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="F106" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B107" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C107" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="D107" s="34">
+        <v>1</v>
+      </c>
+      <c r="E107" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="F107" s="35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C108" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="D108" s="34">
+        <v>200</v>
+      </c>
+      <c r="E108" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="F108" s="35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B109" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C109" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D109" s="34">
+        <v>200</v>
+      </c>
+      <c r="E109" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="F109" s="35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B110" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C110" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D110" s="34">
+        <v>35</v>
+      </c>
+      <c r="E110" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="F110" s="35" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B111" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C111" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="D111" s="34">
+        <v>15</v>
+      </c>
+      <c r="E111" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="F111" s="35" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B112" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C112" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D112" s="34">
+        <v>2</v>
+      </c>
+      <c r="E112" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="F112" s="35" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B113" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="D113" s="34">
+        <v>1</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="F113" s="35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="D114" s="34">
+        <v>2</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="F114" s="35" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B115" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="C115" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="D115" s="34">
+        <v>70</v>
+      </c>
+      <c r="E115" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="F115" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B116" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C116" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="D116" s="34">
+        <v>100</v>
+      </c>
+      <c r="E116" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="F116" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B117" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C117" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="D117" s="34">
+        <v>50</v>
+      </c>
+      <c r="E117" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="F117" s="35" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B118" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C118" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D118" s="34">
+        <v>50</v>
+      </c>
+      <c r="E118" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F118" s="35" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B119" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C119" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="D119" s="34">
+        <v>90</v>
+      </c>
+      <c r="E119" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="F119" s="35" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C120" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="D120" s="34">
+        <v>50</v>
+      </c>
+      <c r="E120" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="F120" s="35" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B121" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C121" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="D121" s="34">
+        <v>150</v>
+      </c>
+      <c r="E121" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="F121" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B122" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C122" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="D122" s="34">
+        <v>50</v>
+      </c>
+      <c r="E122" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="F122" s="35" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B123" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C123" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="D123" s="34">
+        <v>20</v>
+      </c>
+      <c r="E123" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="F123" s="35" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B124" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="D124" s="34">
+        <v>30</v>
+      </c>
+      <c r="E124" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="F124" s="35" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B125" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C125" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="D125" s="34">
+        <v>20</v>
+      </c>
+      <c r="E125" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="F125" s="35" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C126" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="D126" s="34">
+        <v>10</v>
+      </c>
+      <c r="E126" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="F126" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B127" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C127" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="D127" s="34">
+        <v>10</v>
+      </c>
+      <c r="E127" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="F127" s="35" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B128" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C128" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="D128" s="34">
+        <v>2</v>
+      </c>
+      <c r="E128" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="F128" s="35" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B129" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C129" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D129" s="34">
+        <v>20</v>
+      </c>
+      <c r="E129" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="F129" s="35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B130" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C130" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="D130" s="34">
+        <v>2</v>
+      </c>
+      <c r="E130" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="F130" s="35" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B131" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C131" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="D131" s="34">
+        <v>3</v>
+      </c>
+      <c r="E131" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="F131" s="35" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="C132" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="D132" s="34">
+        <v>3</v>
+      </c>
+      <c r="E132" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="F132" s="35" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B133" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C133" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="D133" s="34">
+        <v>40</v>
+      </c>
+      <c r="E133" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F133" s="35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B134" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C134" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="D134" s="34">
+        <v>20</v>
+      </c>
+      <c r="E134" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F134" s="35" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B135" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C135" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="D135" s="34">
+        <v>10</v>
+      </c>
+      <c r="E135" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="F135" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B136" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C136" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="D136" s="34">
+        <v>5</v>
+      </c>
+      <c r="E136" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="F136" s="35" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B137" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C137" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="D137" s="34">
+        <v>5</v>
+      </c>
+      <c r="E137" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F137" s="35" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="C138" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="D138" s="34">
+        <v>4</v>
+      </c>
+      <c r="E138" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="F138" s="35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B139" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="C139" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="D139" s="34">
+        <v>2</v>
+      </c>
+      <c r="E139" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="F139" s="35" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B140" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="C140" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="D140" s="34">
+        <v>15</v>
+      </c>
+      <c r="E140" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="F140" s="35" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B141" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C141" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="D141" s="34">
+        <v>5</v>
+      </c>
+      <c r="E141" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="F141" s="35" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B142" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="C142" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="D142" s="34">
+        <v>1500</v>
+      </c>
+      <c r="E142" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="F142" s="35" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B143" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C143" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D143" s="34">
+        <v>10</v>
+      </c>
+      <c r="E143" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="F143" s="35" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C144" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="D144" s="34">
+        <v>5</v>
+      </c>
+      <c r="E144" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="F144" s="35" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B145" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="C145" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="D145" s="34">
+        <v>200</v>
+      </c>
+      <c r="E145" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="F145" s="35" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="C146" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="D146" s="39">
+        <v>50</v>
+      </c>
+      <c r="E146" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="F146" s="40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B147" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="C147" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="D147" s="39">
+        <v>150</v>
+      </c>
+      <c r="E147" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="F147" s="40" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B148" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="C148" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="D148" s="39">
+        <v>60</v>
+      </c>
+      <c r="E148" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="F148" s="40" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B149" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="C149" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="D149" s="39">
+        <v>1</v>
+      </c>
+      <c r="E149" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="F149" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B150" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="C150" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="D150" s="39">
+        <v>3</v>
+      </c>
+      <c r="E150" s="36" t="s">
+        <v>337</v>
+      </c>
+      <c r="F150" s="40" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B151" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="C151" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="D151" s="39">
+        <v>10</v>
+      </c>
+      <c r="E151" s="36" t="s">
+        <v>341</v>
+      </c>
+      <c r="F151" s="40" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B152" s="37" t="s">
+        <v>343</v>
+      </c>
+      <c r="C152" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="D152" s="39">
+        <v>3</v>
+      </c>
+      <c r="E152" s="36" t="s">
+        <v>345</v>
+      </c>
+      <c r="F152" s="40" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B153" s="37" t="s">
+        <v>343</v>
+      </c>
+      <c r="C153" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="D153" s="39">
+        <v>4</v>
+      </c>
+      <c r="E153" s="36" t="s">
+        <v>347</v>
+      </c>
+      <c r="F153" s="40" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B154" s="37" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="D154" s="39">
+        <v>1</v>
+      </c>
+      <c r="E154" s="36" t="s">
+        <v>350</v>
+      </c>
+      <c r="F154" s="40" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B155" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="C155" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="D155" s="39">
+        <v>60</v>
+      </c>
+      <c r="E155" s="36" t="s">
+        <v>354</v>
+      </c>
+      <c r="F155" s="40" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B156" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="C156" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="D156" s="39">
+        <v>40</v>
+      </c>
+      <c r="E156" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="F156" s="40" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B157" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="C157" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="D157" s="39">
+        <v>5</v>
+      </c>
+      <c r="E157" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="F157" s="40" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B158" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="C158" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="D158" s="39">
+        <v>100</v>
+      </c>
+      <c r="E158" s="36" t="s">
+        <v>363</v>
+      </c>
+      <c r="F158" s="40" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B159" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C159" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="D159" s="39">
+        <v>1</v>
+      </c>
+      <c r="E159" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="F159" s="40" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B160" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="C160" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="D160" s="39">
+        <v>100</v>
+      </c>
+      <c r="E160" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="F160" s="40" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B161" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C161" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="D161" s="39">
+        <v>150</v>
+      </c>
+      <c r="E161" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="F161" s="40" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B162" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C162" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="D162" s="39">
+        <v>50</v>
+      </c>
+      <c r="E162" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="F162" s="40" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B163" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C163" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="D163" s="39">
+        <v>120</v>
+      </c>
+      <c r="E163" s="36" t="s">
+        <v>378</v>
+      </c>
+      <c r="F163" s="40" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B164" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C164" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="D164" s="39">
+        <v>70</v>
+      </c>
+      <c r="E164" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="F164" s="40" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B165" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C165" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="D165" s="39">
+        <v>50</v>
+      </c>
+      <c r="E165" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="F165" s="40" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B166" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C166" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="D166" s="39">
+        <v>50</v>
+      </c>
+      <c r="E166" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="F166" s="40" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B167" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C167" s="38" t="s">
+        <v>389</v>
+      </c>
+      <c r="D167" s="39">
+        <v>50</v>
+      </c>
+      <c r="E167" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="F167" s="40" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B168" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C168" s="38" t="s">
+        <v>392</v>
+      </c>
+      <c r="D168" s="39">
+        <v>50</v>
+      </c>
+      <c r="E168" s="36" t="s">
+        <v>393</v>
+      </c>
+      <c r="F168" s="40" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B169" s="37" t="s">
+        <v>395</v>
+      </c>
+      <c r="C169" s="38" t="s">
+        <v>396</v>
+      </c>
+      <c r="D169" s="39">
+        <v>25</v>
+      </c>
+      <c r="E169" s="36" t="s">
+        <v>397</v>
+      </c>
+      <c r="F169" s="40" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B170" s="37" t="s">
+        <v>395</v>
+      </c>
+      <c r="C170" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="D170" s="39">
+        <v>50</v>
+      </c>
+      <c r="E170" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="F170" s="40" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B171" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="C171" s="38" t="s">
+        <v>402</v>
+      </c>
+      <c r="D171" s="39">
+        <v>10</v>
+      </c>
+      <c r="E171" s="36" t="s">
+        <v>403</v>
+      </c>
+      <c r="F171" s="40" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B172" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="C172" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="D172" s="39">
+        <v>10</v>
+      </c>
+      <c r="E172" s="36" t="s">
+        <v>405</v>
+      </c>
+      <c r="F172" s="40" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B173" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="C173" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="D173" s="39">
+        <v>10</v>
+      </c>
+      <c r="E173" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="F173" s="40" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B174" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="C174" s="38" t="s">
+        <v>410</v>
+      </c>
+      <c r="D174" s="39">
+        <v>500</v>
+      </c>
+      <c r="E174" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="F174" s="40" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B175" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="C175" s="38" t="s">
+        <v>414</v>
+      </c>
+      <c r="D175" s="39">
+        <v>5</v>
+      </c>
+      <c r="E175" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="F175" s="40" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B176" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="C176" s="38" t="s">
+        <v>417</v>
+      </c>
+      <c r="D176" s="39">
+        <v>10</v>
+      </c>
+      <c r="E176" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="F176" s="40" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B177" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="C177" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="D177" s="44">
+        <v>5</v>
+      </c>
+      <c r="E177" s="41" t="s">
+        <v>422</v>
+      </c>
+      <c r="F177" s="45" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B178" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="C178" s="43" t="s">
+        <v>423</v>
+      </c>
+      <c r="D178" s="44">
+        <v>3</v>
+      </c>
+      <c r="E178" s="41" t="s">
+        <v>424</v>
+      </c>
+      <c r="F178" s="45" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B179" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="C179" s="43" t="s">
+        <v>427</v>
+      </c>
+      <c r="D179" s="44">
+        <v>1</v>
+      </c>
+      <c r="E179" s="41" t="s">
+        <v>428</v>
+      </c>
+      <c r="F179" s="45" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B180" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C180" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="D180" s="44">
+        <v>3</v>
+      </c>
+      <c r="E180" s="41" t="s">
+        <v>430</v>
+      </c>
+      <c r="F180" s="45" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B181" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="C181" s="43" t="s">
+        <v>433</v>
+      </c>
+      <c r="D181" s="44">
+        <v>50</v>
+      </c>
+      <c r="E181" s="41" t="s">
+        <v>434</v>
+      </c>
+      <c r="F181" s="45" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B182" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="C182" s="43" t="s">
+        <v>436</v>
+      </c>
+      <c r="D182" s="44">
+        <v>20</v>
+      </c>
+      <c r="E182" s="41" t="s">
+        <v>437</v>
+      </c>
+      <c r="F182" s="45" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B183" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C183" s="43" t="s">
+        <v>440</v>
+      </c>
+      <c r="D183" s="44">
+        <v>15</v>
+      </c>
+      <c r="E183" s="41" t="s">
+        <v>441</v>
+      </c>
+      <c r="F183" s="45" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B184" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C184" s="43" t="s">
+        <v>443</v>
+      </c>
+      <c r="D184" s="44">
+        <v>5</v>
+      </c>
+      <c r="E184" s="41" t="s">
+        <v>444</v>
+      </c>
+      <c r="F184" s="45" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B185" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C185" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="D185" s="44">
+        <v>3</v>
+      </c>
+      <c r="E185" s="41" t="s">
+        <v>446</v>
+      </c>
+      <c r="F185" s="45" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B186" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="C186" s="48" t="s">
+        <v>449</v>
+      </c>
+      <c r="D186" s="49">
+        <v>50</v>
+      </c>
+      <c r="E186" s="46" t="s">
+        <v>450</v>
+      </c>
+      <c r="F186" s="50" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B187" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="C187" s="48" t="s">
+        <v>452</v>
+      </c>
+      <c r="D187" s="49">
+        <v>30</v>
+      </c>
+      <c r="E187" s="46" t="s">
+        <v>453</v>
+      </c>
+      <c r="F187" s="50" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B188" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="C188" s="48" t="s">
+        <v>455</v>
+      </c>
+      <c r="D188" s="49">
+        <v>20</v>
+      </c>
+      <c r="E188" s="46" t="s">
+        <v>456</v>
+      </c>
+      <c r="F188" s="50" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B189" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="C189" s="48" t="s">
+        <v>457</v>
+      </c>
+      <c r="D189" s="49">
+        <v>5</v>
+      </c>
+      <c r="E189" s="46" t="s">
+        <v>458</v>
+      </c>
+      <c r="F189" s="50" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B190" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="C190" s="48" t="s">
+        <v>459</v>
+      </c>
+      <c r="D190" s="49">
+        <v>12</v>
+      </c>
+      <c r="E190" s="46" t="s">
+        <v>460</v>
+      </c>
+      <c r="F190" s="50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B191" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="C191" s="48" t="s">
+        <v>462</v>
+      </c>
+      <c r="D191" s="49">
+        <v>4</v>
+      </c>
+      <c r="E191" s="46" t="s">
+        <v>463</v>
+      </c>
+      <c r="F191" s="50" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B192" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="C192" s="48" t="s">
+        <v>464</v>
+      </c>
+      <c r="D192" s="49">
+        <v>8</v>
+      </c>
+      <c r="E192" s="46" t="s">
+        <v>465</v>
+      </c>
+      <c r="F192" s="50" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B193" s="47" t="s">
+        <v>467</v>
+      </c>
+      <c r="C193" s="48" t="s">
+        <v>468</v>
+      </c>
+      <c r="D193" s="49">
+        <v>20</v>
+      </c>
+      <c r="E193" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="F193" s="50" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B194" s="47" t="s">
+        <v>467</v>
+      </c>
+      <c r="C194" s="48" t="s">
+        <v>470</v>
+      </c>
+      <c r="D194" s="49">
+        <v>30</v>
+      </c>
+      <c r="E194" s="46" t="s">
+        <v>471</v>
+      </c>
+      <c r="F194" s="50" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B195" s="47" t="s">
+        <v>467</v>
+      </c>
+      <c r="C195" s="48" t="s">
+        <v>473</v>
+      </c>
+      <c r="D195" s="49">
+        <v>10</v>
+      </c>
+      <c r="E195" s="46" t="s">
+        <v>474</v>
+      </c>
+      <c r="F195" s="50" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="197" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B197" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C197" s="51" t="s">
+        <v>476</v>
+      </c>
+      <c r="D197" s="51" t="s">
+        <v>477</v>
+      </c>
+      <c r="E197" s="51" t="s">
+        <v>478</v>
+      </c>
+      <c r="F197" s="51" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B198" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="C198" s="53" t="s">
+        <v>480</v>
+      </c>
+      <c r="D198" s="54">
+        <v>200</v>
+      </c>
+      <c r="E198" s="55" t="s">
+        <v>481</v>
+      </c>
+      <c r="F198" s="56" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B199" s="57" t="s">
+        <v>314</v>
+      </c>
+      <c r="C199" s="58" t="s">
+        <v>483</v>
+      </c>
+      <c r="D199" s="59">
+        <v>15</v>
+      </c>
+      <c r="E199" s="60" t="s">
+        <v>484</v>
+      </c>
+      <c r="F199" s="61" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B200" s="52" t="s">
+        <v>306</v>
+      </c>
+      <c r="C200" s="53" t="s">
+        <v>485</v>
+      </c>
+      <c r="D200" s="54">
+        <v>11</v>
+      </c>
+      <c r="E200" s="55" t="s">
+        <v>486</v>
+      </c>
+      <c r="F200" s="56" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B201" s="57" t="s">
+        <v>487</v>
+      </c>
+      <c r="C201" s="58" t="s">
+        <v>488</v>
+      </c>
+      <c r="D201" s="59">
+        <v>25</v>
+      </c>
+      <c r="E201" s="60" t="s">
+        <v>489</v>
+      </c>
+      <c r="F201" s="61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B202" s="52" t="s">
+        <v>487</v>
+      </c>
+      <c r="C202" s="53" t="s">
+        <v>490</v>
+      </c>
+      <c r="D202" s="54">
+        <v>25</v>
+      </c>
+      <c r="E202" s="55" t="s">
+        <v>491</v>
+      </c>
+      <c r="F202" s="56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B203" s="57" t="s">
+        <v>492</v>
+      </c>
+      <c r="C203" s="58" t="s">
+        <v>493</v>
+      </c>
+      <c r="D203" s="59">
+        <v>50</v>
+      </c>
+      <c r="E203" s="60" t="s">
+        <v>494</v>
+      </c>
+      <c r="F203" s="61" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B204" s="52" t="s">
+        <v>492</v>
+      </c>
+      <c r="C204" s="53" t="s">
+        <v>495</v>
+      </c>
+      <c r="D204" s="54">
+        <v>25</v>
+      </c>
+      <c r="E204" s="55" t="s">
+        <v>496</v>
+      </c>
+      <c r="F204" s="56" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B205" s="57" t="s">
+        <v>492</v>
+      </c>
+      <c r="C205" s="58" t="s">
+        <v>497</v>
+      </c>
+      <c r="D205" s="59">
+        <v>25</v>
+      </c>
+      <c r="E205" s="60" t="s">
+        <v>498</v>
+      </c>
+      <c r="F205" s="61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B206" s="52" t="s">
+        <v>492</v>
+      </c>
+      <c r="C206" s="53" t="s">
+        <v>499</v>
+      </c>
+      <c r="D206" s="54">
+        <v>25</v>
+      </c>
+      <c r="E206" s="55" t="s">
+        <v>500</v>
+      </c>
+      <c r="F206" s="56" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B207" s="57" t="s">
+        <v>492</v>
+      </c>
+      <c r="C207" s="58" t="s">
+        <v>501</v>
+      </c>
+      <c r="D207" s="59">
+        <v>25</v>
+      </c>
+      <c r="E207" s="60" t="s">
+        <v>502</v>
+      </c>
+      <c r="F207" s="61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B208" s="52" t="s">
+        <v>503</v>
+      </c>
+      <c r="C208" s="53" t="s">
+        <v>504</v>
+      </c>
+      <c r="D208" s="54">
+        <v>30</v>
+      </c>
+      <c r="E208" s="55" t="s">
+        <v>505</v>
+      </c>
+      <c r="F208" s="56" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="209" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B209" s="57" t="s">
+        <v>503</v>
+      </c>
+      <c r="C209" s="58" t="s">
+        <v>507</v>
+      </c>
+      <c r="D209" s="59">
+        <v>10</v>
+      </c>
+      <c r="E209" s="60" t="s">
+        <v>508</v>
+      </c>
+      <c r="F209" s="61" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B210" s="52" t="s">
+        <v>503</v>
+      </c>
+      <c r="C210" s="53" t="s">
+        <v>510</v>
+      </c>
+      <c r="D210" s="54">
+        <v>40</v>
+      </c>
+      <c r="E210" s="55" t="s">
+        <v>511</v>
+      </c>
+      <c r="F210" s="56" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="211" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B211" s="57" t="s">
+        <v>512</v>
+      </c>
+      <c r="C211" s="58" t="s">
+        <v>513</v>
+      </c>
+      <c r="D211" s="59">
+        <v>29</v>
+      </c>
+      <c r="E211" s="60" t="s">
+        <v>514</v>
+      </c>
+      <c r="F211" s="61" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B212" s="57" t="s">
+        <v>516</v>
+      </c>
+      <c r="C212" s="58" t="s">
+        <v>517</v>
+      </c>
+      <c r="D212" s="59">
+        <v>69</v>
+      </c>
+      <c r="E212" s="60" t="s">
+        <v>518</v>
+      </c>
+      <c r="F212" s="61" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B213" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="C213" s="58" t="s">
+        <v>520</v>
+      </c>
+      <c r="D213" s="59">
+        <v>30</v>
+      </c>
+      <c r="E213" s="60" t="s">
+        <v>521</v>
+      </c>
+      <c r="F213" s="61" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B214" s="52" t="s">
+        <v>272</v>
+      </c>
+      <c r="C214" s="53" t="s">
+        <v>523</v>
+      </c>
+      <c r="D214" s="54">
+        <v>10</v>
+      </c>
+      <c r="E214" s="55" t="s">
+        <v>524</v>
+      </c>
+      <c r="F214" s="56" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B215" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="C215" s="58" t="s">
+        <v>525</v>
+      </c>
+      <c r="D215" s="59">
+        <v>90</v>
+      </c>
+      <c r="E215" s="60" t="s">
+        <v>526</v>
+      </c>
+      <c r="F215" s="61" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="216" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B216" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="C216" s="53" t="s">
+        <v>528</v>
+      </c>
+      <c r="D216" s="54">
+        <v>90</v>
+      </c>
+      <c r="E216" s="55" t="s">
+        <v>529</v>
+      </c>
+      <c r="F216" s="56" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B217" s="57" t="s">
+        <v>530</v>
+      </c>
+      <c r="C217" s="58" t="s">
+        <v>531</v>
+      </c>
+      <c r="D217" s="59">
+        <v>1</v>
+      </c>
+      <c r="E217" s="60" t="s">
+        <v>532</v>
+      </c>
+      <c r="F217" s="61" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B218" s="52" t="s">
+        <v>530</v>
+      </c>
+      <c r="C218" s="53" t="s">
+        <v>533</v>
+      </c>
+      <c r="D218" s="54">
+        <v>4</v>
+      </c>
+      <c r="E218" s="55" t="s">
+        <v>534</v>
+      </c>
+      <c r="F218" s="56" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="219" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B219" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="C219" s="58" t="s">
+        <v>536</v>
+      </c>
+      <c r="D219" s="59">
+        <v>300</v>
+      </c>
+      <c r="E219" s="60" t="s">
+        <v>537</v>
+      </c>
+      <c r="F219" s="61" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="220" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B220" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="C220" s="53" t="s">
+        <v>539</v>
+      </c>
+      <c r="D220" s="54">
+        <v>200</v>
+      </c>
+      <c r="E220" s="55" t="s">
+        <v>540</v>
+      </c>
+      <c r="F220" s="56" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="221" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B221" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="C221" s="58" t="s">
+        <v>542</v>
+      </c>
+      <c r="D221" s="59">
+        <v>80</v>
+      </c>
+      <c r="E221" s="60" t="s">
+        <v>543</v>
+      </c>
+      <c r="F221" s="61" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="222" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B222" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="C222" s="53" t="s">
+        <v>545</v>
+      </c>
+      <c r="D222" s="54">
+        <v>100</v>
+      </c>
+      <c r="E222" s="55" t="s">
+        <v>546</v>
+      </c>
+      <c r="F222" s="56" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="223" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B223" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="C223" s="58" t="s">
+        <v>547</v>
+      </c>
+      <c r="D223" s="59">
+        <v>100</v>
+      </c>
+      <c r="E223" s="60" t="s">
+        <v>548</v>
+      </c>
+      <c r="F223" s="61" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="224" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B224" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="C224" s="53" t="s">
+        <v>550</v>
+      </c>
+      <c r="D224" s="54">
+        <v>37</v>
+      </c>
+      <c r="E224" s="55" t="s">
+        <v>551</v>
+      </c>
+      <c r="F224" s="56" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="225" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B225" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="C225" s="58" t="s">
+        <v>553</v>
+      </c>
+      <c r="D225" s="59">
+        <v>3</v>
+      </c>
+      <c r="E225" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="F225" s="61" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B226" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="C226" s="53" t="s">
+        <v>556</v>
+      </c>
+      <c r="D226" s="54">
+        <v>25</v>
+      </c>
+      <c r="E226" s="55" t="s">
+        <v>557</v>
+      </c>
+      <c r="F226" s="56" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B227" s="57" t="s">
+        <v>339</v>
+      </c>
+      <c r="C227" s="58" t="s">
+        <v>559</v>
+      </c>
+      <c r="D227" s="59">
+        <v>40</v>
+      </c>
+      <c r="E227" s="60" t="s">
+        <v>560</v>
+      </c>
+      <c r="F227" s="61" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="228" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B228" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="C228" s="53" t="s">
+        <v>562</v>
+      </c>
+      <c r="D228" s="54">
+        <v>14</v>
+      </c>
+      <c r="E228" s="55" t="s">
+        <v>563</v>
+      </c>
+      <c r="F228" s="56" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="229" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B229" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="C229" s="58" t="s">
+        <v>565</v>
+      </c>
+      <c r="D229" s="59">
+        <v>50</v>
+      </c>
+      <c r="E229" s="60" t="s">
+        <v>566</v>
+      </c>
+      <c r="F229" s="61" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B230" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="C230" s="53" t="s">
+        <v>568</v>
+      </c>
+      <c r="D230" s="54">
+        <v>100</v>
+      </c>
+      <c r="E230" s="55" t="s">
+        <v>569</v>
+      </c>
+      <c r="F230" s="56" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="231" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B231" s="57" t="s">
+        <v>401</v>
+      </c>
+      <c r="C231" s="58" t="s">
+        <v>571</v>
+      </c>
+      <c r="D231" s="59">
+        <v>20</v>
+      </c>
+      <c r="E231" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="F231" s="61" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="232" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B232" s="52" t="s">
+        <v>401</v>
+      </c>
+      <c r="C232" s="53" t="s">
+        <v>574</v>
+      </c>
+      <c r="D232" s="54">
+        <v>30</v>
+      </c>
+      <c r="E232" s="55" t="s">
+        <v>575</v>
+      </c>
+      <c r="F232" s="56" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="233" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B233" s="57" t="s">
+        <v>401</v>
+      </c>
+      <c r="C233" s="58" t="s">
+        <v>576</v>
+      </c>
+      <c r="D233" s="59">
+        <v>30</v>
+      </c>
+      <c r="E233" s="60" t="s">
+        <v>577</v>
+      </c>
+      <c r="F233" s="61" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="234" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B234" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="C234" s="53" t="s">
+        <v>523</v>
+      </c>
+      <c r="D234" s="54">
+        <v>5</v>
+      </c>
+      <c r="E234" s="55" t="s">
+        <v>579</v>
+      </c>
+      <c r="F234" s="56" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="235" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B235" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="C235" s="58" t="s">
+        <v>581</v>
+      </c>
+      <c r="D235" s="59">
+        <v>200</v>
+      </c>
+      <c r="E235" s="60" t="s">
+        <v>582</v>
+      </c>
+      <c r="F235" s="61" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="236" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B236" s="52" t="s">
+        <v>467</v>
+      </c>
+      <c r="C236" s="53" t="s">
+        <v>584</v>
+      </c>
+      <c r="D236" s="54">
+        <v>10</v>
+      </c>
+      <c r="E236" s="55" t="s">
+        <v>585</v>
+      </c>
+      <c r="F236" s="56" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="237" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B237" s="57" t="s">
+        <v>467</v>
+      </c>
+      <c r="C237" s="58" t="s">
+        <v>586</v>
+      </c>
+      <c r="D237" s="59">
+        <v>9</v>
+      </c>
+      <c r="E237" s="60" t="s">
+        <v>587</v>
+      </c>
+      <c r="F237" s="61" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B238" s="52" t="s">
+        <v>467</v>
+      </c>
+      <c r="C238" s="53" t="s">
+        <v>589</v>
+      </c>
+      <c r="D238" s="54">
+        <v>60</v>
+      </c>
+      <c r="E238" s="55" t="s">
+        <v>590</v>
+      </c>
+      <c r="F238" s="56" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="239" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B239" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="C239" s="58" t="s">
+        <v>592</v>
+      </c>
+      <c r="D239" s="59">
+        <v>2</v>
+      </c>
+      <c r="E239" s="60" t="s">
+        <v>593</v>
+      </c>
+      <c r="F239" s="61" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="240" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B240" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="C240" s="53" t="s">
+        <v>594</v>
+      </c>
+      <c r="D240" s="54">
+        <v>2</v>
+      </c>
+      <c r="E240" s="55" t="s">
+        <v>595</v>
+      </c>
+      <c r="F240" s="56" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="241" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B241" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="C241" s="58" t="s">
+        <v>596</v>
+      </c>
+      <c r="D241" s="59">
+        <v>2</v>
+      </c>
+      <c r="E241" s="60" t="s">
+        <v>597</v>
+      </c>
+      <c r="F241" s="61" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="242" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B242" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="C242" s="53" t="s">
+        <v>598</v>
+      </c>
+      <c r="D242" s="54">
+        <v>20</v>
+      </c>
+      <c r="E242" s="55" t="s">
+        <v>599</v>
+      </c>
+      <c r="F242" s="56" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="243" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B243" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="C243" s="58" t="s">
+        <v>600</v>
+      </c>
+      <c r="D243" s="59">
+        <v>30</v>
+      </c>
+      <c r="E243" s="60" t="s">
+        <v>601</v>
+      </c>
+      <c r="F243" s="61" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="244" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B244" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="C244" s="53" t="s">
+        <v>602</v>
+      </c>
+      <c r="D244" s="54">
+        <v>50</v>
+      </c>
+      <c r="E244" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="F244" s="56" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="245" spans="2:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B245" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="C245" s="58" t="s">
+        <v>604</v>
+      </c>
+      <c r="D245" s="59">
+        <v>50</v>
+      </c>
+      <c r="E245" s="60" t="s">
+        <v>605</v>
+      </c>
+      <c r="F245" s="61" t="s">
+        <v>583</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:B245" xr:uid="{BDEAB589-59D4-402D-A28C-AA7262E65C2C}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="CDSL"/>
+        <filter val="CDSLEQ"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>